--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/anova_env.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>563.79</v>
+        <v>284.06</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>201.64</v>
+        <v>423.45</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>76.89</v>
+        <v>16.77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.19 ± 0.57</t>
+          <t>2.61 ± 0.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.25 ± 0.39</t>
+          <t>8.21 ± 0.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.18 ± 0.39</t>
+          <t>3.51 ± 0.73</t>
         </is>
       </c>
     </row>
@@ -535,38 +535,38 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.98</v>
+        <v>3.12</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81</v>
+        <v>20.9</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>13.05</v>
+        <v>3.74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0308*</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.83 ± 0.23</t>
+          <t>1.27 ± 0.10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.04 ± 0.11</t>
+          <t>0.83 ± 0.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.74 ± 0.04</t>
+          <t>1.45 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.53</v>
+        <v>12.67</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>122.58</v>
+        <v>265.4</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>4.16</v>
+        <v>1.19</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0208*</t>
+          <t>0.3117</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.13 ± 0.32</t>
+          <t>19.72 ± 0.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.45 ± 0.31</t>
+          <t>18.80 ± 0.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>9.53 ± 0.36</t>
+          <t>20.04 ± 0.65</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.51</v>
+        <v>1.81</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>268.27</v>
+        <v>139.21</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>3.54</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0359*</t>
+          <t>0.7236</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18.35 ± 0.49</t>
+          <t>2.16 ± 0.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.55 ± 0.41</t>
+          <t>1.79 ± 0.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20.47 ± 0.59</t>
+          <t>2.25 ± 0.45</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.01</v>
+        <v>0.38</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>130.32</v>
+        <v>132.86</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.9318</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.28 ± 0.40</t>
+          <t>9.14 ± 0.30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.61 ± 0.25</t>
+          <t>9.12 ± 0.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.59 ± 0.44</t>
+          <t>9.31 ± 0.41</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
